--- a/scripts/checks/results/HLR_results_07_Dunn_fams_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_07_Dunn_fams_noLgArea_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>539</v>
+        <v>662</v>
       </c>
       <c r="E2" t="n">
-        <v>537</v>
+        <v>660</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3002424530370029</v>
+        <v>0.2235251913827403</v>
       </c>
       <c r="H2" t="n">
-        <v>230.4086579424865</v>
+        <v>189.9953799857627</v>
       </c>
       <c r="I2" t="n">
-        <v>1.460779915114385e-43</v>
+        <v>3.606805372741333e-38</v>
       </c>
       <c r="J2" t="n">
-        <v>71.15456703886447</v>
+        <v>91.34369889831773</v>
       </c>
       <c r="K2" t="n">
-        <v>101.6846011131726</v>
+        <v>117.6389728096677</v>
       </c>
       <c r="L2" t="n">
-        <v>30.53003407430809</v>
+        <v>26.29527391134995</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1325038492343845</v>
+        <v>0.1383995437853299</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1890048347828486</v>
+        <v>0.1779712145380752</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.8158622228498638, 'N1ratio-ArgsPreds': -0.23974231781280247}</t>
+          <t>{'const': 0.6122542310653039, 'N1ratio-ArgsPreds': -2.3586335149019666}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 3.861723678139761e-68, 'N1ratio-ArgsPreds': 1.4607799151140621e-43}</t>
+          <t>{'const': 7.046203500856338e-68, 'N1ratio-ArgsPreds': 3.606805372740735e-38}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5479438411342928}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47278450839969377}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5479438411342936)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5479438411342935)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(30.024245303700386)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.352519138274157)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -632,76 +632,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>539</v>
+        <v>662</v>
       </c>
       <c r="E3" t="n">
-        <v>536</v>
+        <v>659</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3677103009192324</v>
+        <v>0.3226902160246737</v>
       </c>
       <c r="H3" t="n">
-        <v>155.8563436817371</v>
+        <v>156.9834493694593</v>
       </c>
       <c r="I3" t="n">
-        <v>4.420959780259847e-54</v>
+        <v>1.755624193101927e-56</v>
       </c>
       <c r="J3" t="n">
-        <v>64.29412583899577</v>
+        <v>79.67802726079529</v>
       </c>
       <c r="K3" t="n">
-        <v>101.6846011131726</v>
+        <v>117.6389728096677</v>
       </c>
       <c r="L3" t="n">
-        <v>18.6952376370884</v>
+        <v>18.98047277443619</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1199517273115593</v>
+        <v>0.1209074768752584</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1890048347828486</v>
+        <v>0.1779712145380752</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.9279371858966083, 'N1ratio-ArgsPreds': -0.2281861069604998, 'Fam_class': -0.0038435901923523676}</t>
+          <t>{'const': 0.7605153950917698, 'N1ratio-ArgsPreds': -2.2157716072717006, 'Fam_class': -0.003999273368872975}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 8.445221960703667e-80, 'N1ratio-ArgsPreds': 3.2528421283290984e-43, 'Fam_class': 1.727350341704145e-13}</t>
+          <t>{'const': 2.8545825977272187e-87, 'N1ratio-ArgsPreds': 3.175014812446558e-38, 'Fam_class': 2.411584701137712e-21}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5215315055018624, 'Fam_class': -0.2610851572874029}</t>
+          <t>{'N1ratio-ArgsPreds': -0.444148055834563, 'Fam_class': -0.3162041604050294}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5464666253104042), 'Fam_class': np.float64(-0.31050931488820976)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47341546024328685), 'Fam_class': np.float64(-0.35736793026027425)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5188559421197032), 'Fam_class': np.float64(-0.2597457369856707)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4423229238197559), 'Fam_class': np.float64(-0.31490478662912325)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(26.921148867292484), 'Fam_class': np.float64(6.746784788222923)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.56495689364576), 'Fam_class': np.float64(9.916502464193364)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.06746784788222948</v>
+        <v>0.09916502464193344</v>
       </c>
       <c r="V3" t="n">
-        <v>57.19335063887485</v>
+        <v>96.48428648923041</v>
       </c>
       <c r="W3" t="n">
-        <v>1.727350341703133e-13</v>
+        <v>2.411584701138846e-21</v>
       </c>
     </row>
     <row r="4">
@@ -717,76 +717,76 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>539</v>
+        <v>662</v>
       </c>
       <c r="E4" t="n">
-        <v>534</v>
+        <v>657</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4005903060175308</v>
+        <v>0.3604240458296738</v>
       </c>
       <c r="H4" t="n">
-        <v>89.21912072864214</v>
+        <v>92.56078053203107</v>
       </c>
       <c r="I4" t="n">
-        <v>4.847276643202384e-58</v>
+        <v>2.053835398531024e-62</v>
       </c>
       <c r="J4" t="n">
-        <v>60.95073563597622</v>
+        <v>75.23905828236026</v>
       </c>
       <c r="K4" t="n">
-        <v>101.6846011131726</v>
+        <v>117.6389728096677</v>
       </c>
       <c r="L4" t="n">
-        <v>10.18346636929909</v>
+        <v>10.59997863182685</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1141399543744873</v>
+        <v>0.1145191145850232</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1890048347828486</v>
+        <v>0.1779712145380752</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.35904828612513934, 'N1ratio-ArgsPreds': -0.21866633769233734, 'Fam_class': -0.004801562237727103, 'Nlen_freq': 0.07611828320218332, 'Vlen_freq': 0.012626523680419048}</t>
+          <t>{'const': 0.41265723940048116, 'N1ratio-ArgsPreds': -2.103403420243527, 'Fam_class': -0.004804286848670588, 'Nlen_freq': 0.5361456970018827, 'Vlen_freq': 0.43037737841313856}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 0.001631862051986746, 'N1ratio-ArgsPreds': 3.778808095182347e-40, 'Fam_class': 1.7039163878867502e-18, 'Nlen_freq': 0.005144525559856323, 'Vlen_freq': 0.5212157026315589}</t>
+          <t>{'const': 6.198876072031836e-10, 'N1ratio-ArgsPreds': 2.19829456284693e-35, 'Fam_class': 5.718725335271394e-28, 'Nlen_freq': 0.024261501590577984, 'Vlen_freq': 0.0543811839824521}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4997735656141612, 'Fam_class': -0.3261577247638339, 'Nlen_freq': 0.1625262068732417, 'Vlen_freq': 0.036693519982807926}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4216240232842632, 'Fam_class': -0.3798528755629705, 'Nlen_freq': 0.11740713856698046, 'Vlen_freq': 0.09938021652084159}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.529982678591896), 'Fam_class': np.float64(-0.3666156406711892), 'Nlen_freq': np.float64(0.12068811934503737), 'Vlen_freq': np.float64(0.02776687638049897)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4574023433538028), 'Fam_class': np.float64(-0.40903185140754306), 'Nlen_freq': np.float64(0.08776018922411087), 'Vlen_freq': np.float64(0.07497696907825363)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4838640635186266), 'Fam_class': np.float64(-0.3050815957821561), 'Nlen_freq': np.float64(0.09412663791088734), 'Vlen_freq': np.float64(0.02150583913391162)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.41135403368883167), 'Fam_class': np.float64(-0.3584765483219413), 'Nlen_freq': np.float64(0.07045673664381924), 'Vlen_freq': np.float64(0.06013095358378465)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.412443196475753), 'Fam_class': np.float64(9.30747800849869), 'Nlen_freq': np.float64(0.8859823964407293), 'Vlen_freq': np.float64(0.046250111685368446)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(16.921214103207248), 'Fam_class': np.float64(12.850543569681314), 'Nlen_freq': np.float64(0.4964151738496501), 'Vlen_freq': np.float64(0.36157315788952643)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03288000509829836</v>
+        <v>0.03773382980500006</v>
       </c>
       <c r="V4" t="n">
-        <v>14.64601165009256</v>
+        <v>19.38090856936977</v>
       </c>
       <c r="W4" t="n">
-        <v>6.421612284688386e-07</v>
+        <v>6.636202805602026e-09</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_07_Dunn_fams_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_07_Dunn_fams_noLgArea_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2235251913827403</v>
+        <v>0.2127090200070492</v>
       </c>
       <c r="H2" t="n">
-        <v>189.9953799857627</v>
+        <v>178.3177462618833</v>
       </c>
       <c r="I2" t="n">
-        <v>3.606805372741333e-38</v>
+        <v>3.551046890077052e-36</v>
       </c>
       <c r="J2" t="n">
-        <v>91.34369889831773</v>
+        <v>92.1915359049147</v>
       </c>
       <c r="K2" t="n">
-        <v>117.6389728096677</v>
+        <v>117.0996978851963</v>
       </c>
       <c r="L2" t="n">
-        <v>26.29527391134995</v>
+        <v>24.90816198028165</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1383995437853299</v>
+        <v>0.1396841453104768</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1779712145380752</v>
+        <v>0.1771553674511291</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.6122542310653039, 'N1ratio-ArgsPreds': -2.3586335149019666}</t>
+          <t>{'const': 0.5881292512992626, 'N1ratio-ArgsPreds': -2.1993804205042555}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 7.046203500856338e-68, 'N1ratio-ArgsPreds': 3.606805372740735e-38}</t>
+          <t>{'const': 5.747937176790004e-66, 'N1ratio-ArgsPreds': 3.551046890075819e-36}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47278450839969377}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4612038811708435}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4612038811708424)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4727845083996953)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46120388117084227)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.352519138274157)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.27090200070484)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3226902160246737</v>
+        <v>0.3143479930593552</v>
       </c>
       <c r="H3" t="n">
-        <v>156.9834493694593</v>
+        <v>151.0644797427451</v>
       </c>
       <c r="I3" t="n">
-        <v>1.755624193101927e-56</v>
+        <v>9.912567001865083e-55</v>
       </c>
       <c r="J3" t="n">
-        <v>79.67802726079529</v>
+        <v>80.28964286712805</v>
       </c>
       <c r="K3" t="n">
-        <v>117.6389728096677</v>
+        <v>117.0996978851963</v>
       </c>
       <c r="L3" t="n">
-        <v>18.98047277443619</v>
+        <v>18.40502750903415</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1209074768752584</v>
+        <v>0.1218355733947315</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1779712145380752</v>
+        <v>0.1771553674511291</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.7605153950917698, 'N1ratio-ArgsPreds': -2.2157716072717006, 'Fam_class': -0.003999273368872975}</t>
+          <t>{'const': 0.7394023249328201, 'N1ratio-ArgsPreds': -2.0659477516740434, 'Fam_class': -0.004038426249780229}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 2.8545825977272187e-87, 'N1ratio-ArgsPreds': 3.175014812446558e-38, 'Fam_class': 2.411584701137712e-21}</t>
+          <t>{'const': 1.4637857582528483e-85, 'N1ratio-ArgsPreds': 2.738826339175663e-36, 'Fam_class': 1.4195739528652064e-21}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.444148055834563, 'Fam_class': -0.3162041604050294}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4332234262364632, 'Fam_class': -0.3200341839720246}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47341546024328685), 'Fam_class': np.float64(-0.35736793026027425)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46218131171638166), 'Fam_class': np.float64(-0.3593043675180531)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4423229238197559), 'Fam_class': np.float64(-0.31490478662912325)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4315644847816254), 'Fam_class': np.float64(-0.3188086778183845)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.56495689364576), 'Fam_class': np.float64(9.916502464193364)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.62479045248298), 'Fam_class': np.float64(10.16389730523065)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.09916502464193344</v>
+        <v>0.1016389730523061</v>
       </c>
       <c r="V3" t="n">
-        <v>96.48428648923041</v>
+        <v>97.68816041293671</v>
       </c>
       <c r="W3" t="n">
-        <v>2.411584701138846e-21</v>
+        <v>1.419573952864477e-21</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3604240458296738</v>
+        <v>0.350552714844017</v>
       </c>
       <c r="H4" t="n">
-        <v>92.56078053203107</v>
+        <v>88.6573625437525</v>
       </c>
       <c r="I4" t="n">
-        <v>2.053835398531024e-62</v>
+        <v>3.059967298640181e-60</v>
       </c>
       <c r="J4" t="n">
-        <v>75.23905828236026</v>
+        <v>76.05008088412657</v>
       </c>
       <c r="K4" t="n">
-        <v>117.6389728096677</v>
+        <v>117.0996978851963</v>
       </c>
       <c r="L4" t="n">
-        <v>10.59997863182685</v>
+        <v>10.26240425026744</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1145191145850232</v>
+        <v>0.115753547768838</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1779712145380752</v>
+        <v>0.1771553674511291</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.41265723940048116, 'N1ratio-ArgsPreds': -2.103403420243527, 'Fam_class': -0.004804286848670588, 'Nlen_freq': 0.5361456970018827, 'Vlen_freq': 0.43037737841313856}</t>
+          <t>{'const': 0.40897685579672044, 'N1ratio-ArgsPreds': -1.9326919433951646, 'Fam_class': -0.004817669297531588, 'Nlen_freq': 0.3901864530554606, 'Vlen_freq': 0.5433660529807365}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 6.198876072031836e-10, 'N1ratio-ArgsPreds': 2.19829456284693e-35, 'Fam_class': 5.718725335271394e-28, 'Nlen_freq': 0.024261501590577984, 'Vlen_freq': 0.0543811839824521}</t>
+          <t>{'const': 9.165467882330402e-10, 'N1ratio-ArgsPreds': 1.113430375327463e-32, 'Fam_class': 9.929038626680982e-28, 'Nlen_freq': 0.09865445385911518, 'Vlen_freq': 0.014544138670187091}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4216240232842632, 'Fam_class': -0.3798528755629705, 'Nlen_freq': 0.11740713856698046, 'Vlen_freq': 0.09938021652084159}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4052800584616941, 'Fam_class': -0.38178705439191923, 'Nlen_freq': 0.08612906789962384, 'Vlen_freq': 0.12644496525548435}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4574023433538028), 'Fam_class': np.float64(-0.40903185140754306), 'Nlen_freq': np.float64(0.08776018922411087), 'Vlen_freq': np.float64(0.07497696907825363)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44065051163235114), 'Fam_class': np.float64(-0.40733004766158526), 'Nlen_freq': np.float64(0.06438535741418651), 'Vlen_freq': np.float64(0.09515122232539207)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.41135403368883167), 'Fam_class': np.float64(-0.3584765483219413), 'Nlen_freq': np.float64(0.07045673664381924), 'Vlen_freq': np.float64(0.06013095358378465)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.39558998670179335), 'Fam_class': np.float64(-0.3594297045679198), 'Nlen_freq': np.float64(0.05199494378803997), 'Vlen_freq': np.float64(0.07703024450339803)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(16.921214103207248), 'Fam_class': np.float64(12.850543569681314), 'Nlen_freq': np.float64(0.4964151738496501), 'Vlen_freq': np.float64(0.36157315788952643)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(15.649143757872505), 'Fam_class': np.float64(12.91897125257821), 'Nlen_freq': np.float64(0.27034741795214356), 'Vlen_freq': np.float64(0.5933658568253283)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03773382980500006</v>
+        <v>0.03620472178466172</v>
       </c>
       <c r="V4" t="n">
-        <v>19.38090856936977</v>
+        <v>18.31288139637827</v>
       </c>
       <c r="W4" t="n">
-        <v>6.636202805602026e-09</v>
+        <v>1.822177306545835e-08</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_07_Dunn_fams_noLgArea_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_07_Dunn_fams_noLgArea_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2127090200070492</v>
+        <v>0.2126104794529781</v>
       </c>
       <c r="H2" t="n">
-        <v>178.3177462618833</v>
+        <v>178.2128321208532</v>
       </c>
       <c r="I2" t="n">
-        <v>3.551046890077052e-36</v>
+        <v>3.701627190479354e-36</v>
       </c>
       <c r="J2" t="n">
-        <v>92.1915359049147</v>
+        <v>92.20307497402587</v>
       </c>
       <c r="K2" t="n">
         <v>117.0996978851963</v>
       </c>
       <c r="L2" t="n">
-        <v>24.90816198028165</v>
+        <v>24.89662291117048</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1396841453104768</v>
+        <v>0.139701628748524</v>
       </c>
       <c r="N2" t="n">
         <v>0.1771553674511291</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5881292512992626, 'N1ratio-ArgsPreds': -2.1993804205042555}</t>
+          <t>{'const': 0.5877559712647106, 'N1ratio-ArgsPreds': -2.1955128851816026}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 5.747937176790004e-66, 'N1ratio-ArgsPreds': 3.551046890075819e-36}</t>
+          <t>{'const': 5.84595231215245e-66, 'N1ratio-ArgsPreds': 3.701627190478273e-36}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4612038811708435}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46109703908502636}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4612038811708424)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4610970390850252)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46120388117084227)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46109703908502514)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.27090200070484)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.26104794529772)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3143479930593552</v>
+        <v>0.3142536789280335</v>
       </c>
       <c r="H3" t="n">
-        <v>151.0644797427451</v>
+        <v>150.9983852992777</v>
       </c>
       <c r="I3" t="n">
-        <v>9.912567001865083e-55</v>
+        <v>1.037214918238356e-54</v>
       </c>
       <c r="J3" t="n">
-        <v>80.28964286712805</v>
+        <v>80.30068702341214</v>
       </c>
       <c r="K3" t="n">
         <v>117.0996978851963</v>
       </c>
       <c r="L3" t="n">
-        <v>18.40502750903415</v>
+        <v>18.39950543089211</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1218355733947315</v>
+        <v>0.1218523323572263</v>
       </c>
       <c r="N3" t="n">
         <v>0.1771553674511291</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.7394023249328201, 'N1ratio-ArgsPreds': -2.0659477516740434, 'Fam_class': -0.004038426249780229}</t>
+          <t>{'const': 0.7390483146626645, 'N1ratio-ArgsPreds': -2.0622715113437615, 'Fam_class': -0.004038512462715218}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 1.4637857582528483e-85, 'N1ratio-ArgsPreds': 2.738826339175663e-36, 'Fam_class': 1.4195739528652064e-21}</t>
+          <t>{'const': 1.5006787508941505e-85, 'N1ratio-ArgsPreds': 2.8665240304344807e-36, 'Fam_class': 1.425438616316008e-21}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4332234262364632, 'Fam_class': -0.3200341839720246}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4331139635244528, 'Fam_class': -0.3200410161102365}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46218131171638166), 'Fam_class': np.float64(-0.3593043675180531)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4620642748324306), 'Fam_class': np.float64(-0.35928935350513513)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4315644847816254), 'Fam_class': np.float64(-0.3188086778183845)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.43145520091141415), 'Fam_class': np.float64(-0.31881530621200665)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(18.62479045248298), 'Fam_class': np.float64(10.16389730523065)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.615359039350878), 'Fam_class': np.float64(10.164319947505557)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.1016389730523061</v>
+        <v>0.1016431994750554</v>
       </c>
       <c r="V3" t="n">
-        <v>97.68816041293671</v>
+        <v>97.67878644883304</v>
       </c>
       <c r="W3" t="n">
-        <v>1.419573952864477e-21</v>
+        <v>1.425438616308688e-21</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.350552714844017</v>
+        <v>0.3500599767220076</v>
       </c>
       <c r="H4" t="n">
-        <v>88.6573625437525</v>
+        <v>88.46562623824903</v>
       </c>
       <c r="I4" t="n">
-        <v>3.059967298640181e-60</v>
+        <v>3.92022657883522e-60</v>
       </c>
       <c r="J4" t="n">
-        <v>76.05008088412657</v>
+        <v>76.10778036935039</v>
       </c>
       <c r="K4" t="n">
         <v>117.0996978851963</v>
       </c>
       <c r="L4" t="n">
-        <v>10.26240425026744</v>
+        <v>10.24797937896149</v>
       </c>
       <c r="M4" t="n">
-        <v>0.115753547768838</v>
+        <v>0.1158413704251909</v>
       </c>
       <c r="N4" t="n">
         <v>0.1771553674511291</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.40897685579672044, 'N1ratio-ArgsPreds': -1.9326919433951646, 'Fam_class': -0.004817669297531588, 'Nlen_freq': 0.3901864530554606, 'Vlen_freq': 0.5433660529807365}</t>
+          <t>{'const': 0.41067962768320154, 'N1ratio-ArgsPreds': -1.9279878972020177, 'Fam_class': -0.0048145394248503386, 'Nlen_freq': 0.39088151082525746, 'Vlen_freq': 0.5417491361627274}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 9.165467882330402e-10, 'N1ratio-ArgsPreds': 1.113430375327463e-32, 'Fam_class': 9.929038626680982e-28, 'Nlen_freq': 0.09865445385911518, 'Vlen_freq': 0.014544138670187091}</t>
+          <t>{'const': 7.82481925792533e-10, 'N1ratio-ArgsPreds': 1.3830282780199151e-32, 'Fam_class': 1.1348840588563166e-27, 'Nlen_freq': 0.10264354408433572, 'Vlen_freq': 0.014927800375835907}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4052800584616941, 'Fam_class': -0.38178705439191923, 'Nlen_freq': 0.08612906789962384, 'Vlen_freq': 0.12644496525548435}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4049119988280476, 'Fam_class': -0.3815390205818343, 'Nlen_freq': 0.08525387630159485, 'Vlen_freq': 0.12617460326781668}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.44065051163235114), 'Fam_class': np.float64(-0.40733004766158526), 'Nlen_freq': np.float64(0.06438535741418651), 'Vlen_freq': np.float64(0.09515122232539207)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4400501100279178), 'Fam_class': np.float64(-0.4069163105576793), 'Nlen_freq': np.float64(0.06363670000192394), 'Vlen_freq': np.float64(0.09478646843759522)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.39558998670179335), 'Fam_class': np.float64(-0.3594297045679198), 'Nlen_freq': np.float64(0.05199494378803997), 'Vlen_freq': np.float64(0.07703024450339803)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.3950712173183408), 'Fam_class': np.float64(-0.3591282890395734), 'Nlen_freq': np.float64(0.051407376695067036), 'Vlen_freq': np.float64(0.07676137654990321)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(15.649143757872505), 'Fam_class': np.float64(12.91897125257821), 'Nlen_freq': np.float64(0.27034741795214356), 'Vlen_freq': np.float64(0.5933658568253283)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(15.608126675339564), 'Fam_class': np.float64(12.897312798849136), 'Nlen_freq': np.float64(0.26427183786685216), 'Vlen_freq': np.float64(0.5892308929836031)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.03620472178466172</v>
+        <v>0.03580629779397415</v>
       </c>
       <c r="V4" t="n">
-        <v>18.31288139637827</v>
+        <v>18.09762194055482</v>
       </c>
       <c r="W4" t="n">
-        <v>1.822177306545835e-08</v>
+        <v>2.234435104341028e-08</v>
       </c>
     </row>
   </sheetData>
